--- a/docs/shop-products-sample.xlsx
+++ b/docs/shop-products-sample.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="상품" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:G6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -421,9 +421,6 @@
       <c r="G1" t="str">
         <v>카테고리</v>
       </c>
-      <c r="H1" t="str">
-        <v>순서</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -447,9 +444,6 @@
       <c r="G2" t="str">
         <v>러닝화</v>
       </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -473,9 +467,6 @@
       <c r="G3" t="str">
         <v>러닝화</v>
       </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -499,9 +490,6 @@
       <c r="G4" t="str">
         <v>사이클</v>
       </c>
-      <c r="H4">
-        <v>3</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -525,9 +513,6 @@
       <c r="G5" t="str">
         <v>워치</v>
       </c>
-      <c r="H5">
-        <v>4</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -551,13 +536,10 @@
       <c r="G6" t="str">
         <v>액세서리</v>
       </c>
-      <c r="H6">
-        <v>5</v>
-      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G6"/>
   </ignoredErrors>
 </worksheet>
 </file>